--- a/RUN.xlsx
+++ b/RUN.xlsx
@@ -1,214 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\models\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EC761E-6B2D-47E1-A72C-BDA8A683EAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="13080" yWindow="0" windowWidth="25425" windowHeight="20985" activeTab="1" xr2:uid="{E06A6E02-F966-45F3-9FD6-4E3BC889F169}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="13080" yWindow="0" windowWidth="25425" windowHeight="20985" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Main" sheetId="1" r:id="rId1"/>
-    <sheet name="Model" sheetId="2" r:id="rId2"/>
+    <sheet name="Main" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
-  <si>
-    <t>Cash</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Shares</t>
-  </si>
-  <si>
-    <t>Debt</t>
-  </si>
-  <si>
-    <t>EV</t>
-  </si>
-  <si>
-    <t>Mkt Cap</t>
-  </si>
-  <si>
-    <t>Restricted cash - contractually / legally commited to a purpose (debt convenants, etc)</t>
-  </si>
-  <si>
-    <t>Revenue</t>
-  </si>
-  <si>
-    <t>Q12026</t>
-  </si>
-  <si>
-    <t>Q22026</t>
-  </si>
-  <si>
-    <t>Q32026</t>
-  </si>
-  <si>
-    <t>Q42026</t>
-  </si>
-  <si>
-    <t>Q12025</t>
-  </si>
-  <si>
-    <t>Q22025</t>
-  </si>
-  <si>
-    <t>Q32025</t>
-  </si>
-  <si>
-    <t>Q42025</t>
-  </si>
-  <si>
-    <t>Q12027</t>
-  </si>
-  <si>
-    <t>Q22027</t>
-  </si>
-  <si>
-    <t>Q32027</t>
-  </si>
-  <si>
-    <t>Q42027</t>
-  </si>
-  <si>
-    <t>Customer agreements and incentives</t>
-  </si>
-  <si>
-    <t>Energy systems and product sales</t>
-  </si>
-  <si>
-    <t>Revenue y/y</t>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <t>Customer agreements and incentives cost</t>
-  </si>
-  <si>
-    <t>Energy systems and product sales cost</t>
-  </si>
-  <si>
-    <t>S&amp;M</t>
-  </si>
-  <si>
-    <t>G&amp;A</t>
-  </si>
-  <si>
-    <t>Operating Expenses</t>
-  </si>
-  <si>
-    <t>R&amp;D</t>
-  </si>
-  <si>
-    <t>Q12024</t>
-  </si>
-  <si>
-    <t>Q22024</t>
-  </si>
-  <si>
-    <t>Q32024</t>
-  </si>
-  <si>
-    <t>Q42024</t>
-  </si>
-  <si>
-    <t>Interest</t>
-  </si>
-  <si>
-    <t>Other income</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>Operating margin</t>
-  </si>
-  <si>
-    <t>Operating Income</t>
-  </si>
-  <si>
-    <t>Earnings</t>
-  </si>
-  <si>
-    <t>EBT</t>
-  </si>
-  <si>
-    <t>Net loss attributable to noncontrolling interests and redeemable noncontrolling interests is financing structure (tax equity)</t>
-  </si>
-  <si>
-    <t>Shares outstanding</t>
-  </si>
-  <si>
-    <t>Tax rate</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,38 +69,101 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -634,71 +541,91 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A2102B1-3DA0-4149-9E80-4C86183E0177}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="B4:S10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col min="19" max="19" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col width="15.42578125" bestFit="1" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="R5" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="1">
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Restricted cash - contractually / legally commited to a purpose (debt convenants, etc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Net loss attributable to noncontrolling interests and redeemable noncontrolling interests is financing structure (tax equity)</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="n">
         <v>9.26</v>
       </c>
     </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R6" t="s">
-        <v>2</v>
-      </c>
-      <c r="S6" s="2">
+    <row r="6">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="n">
         <v>240846</v>
       </c>
     </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R7" t="s">
-        <v>5</v>
+    <row r="7">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Mkt Cap</t>
+        </is>
       </c>
       <c r="S7" s="2">
         <f>S6*S5</f>
-        <v>2230233.96</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R8" t="s">
-        <v>0</v>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
       </c>
       <c r="S8">
         <f>712+235</f>
-        <v>947</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R9" t="s">
-        <v>3</v>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Debt</t>
+        </is>
       </c>
       <c r="S9">
         <f>321+49+444+154+188</f>
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
-      <c r="R10" t="s">
-        <v>4</v>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>EV</t>
+        </is>
       </c>
       <c r="S10" s="2">
         <f>S7-S8+S9</f>
-        <v>2230442.96</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -707,623 +634,709 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD33CA0F-3FBF-4EAA-ADEE-FACC9C18E806}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AG26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="9.140625" style="3"/>
+    <col width="38.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="9.140625" customWidth="1" style="3" min="3" max="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="C2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="W2">
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Q12024</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>Q22024</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>Q32024</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>Q42024</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Q12025</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>Q22025</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Q32025</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Q42025</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Q12026</t>
+        </is>
+      </c>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>Q22026</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>Q32026</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>Q42026</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Q12027</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Q22027</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>Q32027</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>Q42027</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
         <v>2025</v>
       </c>
-      <c r="X2">
+      <c r="X2" t="n">
         <v>2026</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" t="n">
         <v>2027</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" t="n">
         <v>2028</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" t="n">
         <v>2029</v>
       </c>
-      <c r="AB2">
+      <c r="AB2" t="n">
         <v>2030</v>
       </c>
-      <c r="AC2">
+      <c r="AC2" t="n">
         <v>2031</v>
       </c>
-      <c r="AD2">
+      <c r="AD2" t="n">
         <v>2032</v>
       </c>
-      <c r="AE2">
+      <c r="AE2" t="n">
         <v>2033</v>
       </c>
-      <c r="AF2">
+      <c r="AF2" t="n">
         <v>2034</v>
       </c>
-      <c r="AG2">
+      <c r="AG2" t="n">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>20</v>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Customer agreements and incentives</t>
+        </is>
       </c>
       <c r="G3" s="3">
         <f>861-H3</f>
-        <v>403</v>
-      </c>
-      <c r="H3" s="3">
+        <v/>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>458</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="3" t="n">
         <v>544</v>
       </c>
       <c r="K3" s="3">
         <f>1011-L3</f>
-        <v>467</v>
-      </c>
-      <c r="L3" s="3">
+        <v/>
+      </c>
+      <c r="L3" s="3" t="n">
         <v>544</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>21</v>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Energy systems and product sales</t>
+        </is>
       </c>
       <c r="G4" s="3">
         <f>212-H4</f>
-        <v>101</v>
-      </c>
-      <c r="H4" s="3">
+        <v/>
+      </c>
+      <c r="H4" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="3" t="n">
         <v>326</v>
       </c>
       <c r="K4" s="3">
         <f>581-L4</f>
-        <v>255</v>
-      </c>
-      <c r="L4" s="3">
+        <v/>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>326</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
       <c r="G5" s="7">
         <f>SUM(G3:G4)</f>
-        <v>504</v>
+        <v/>
       </c>
       <c r="H5" s="7">
         <f>SUM(H3:H4)</f>
-        <v>569</v>
-      </c>
-      <c r="I5" s="7"/>
+        <v/>
+      </c>
+      <c r="I5" s="7" t="n"/>
       <c r="J5" s="7">
         <f>SUM(J3:J4)</f>
-        <v>870</v>
+        <v/>
       </c>
       <c r="K5" s="7">
         <f>SUM(K3:K4)</f>
-        <v>722</v>
+        <v/>
       </c>
       <c r="L5" s="7">
         <f>SUM(L3:L4)</f>
-        <v>870</v>
-      </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
-      <c r="S5" s="6"/>
-      <c r="T5" s="6"/>
-      <c r="U5" s="6"/>
-      <c r="V5" s="6"/>
-      <c r="W5" s="6"/>
-      <c r="X5" s="6"/>
-      <c r="Y5" s="6"/>
-      <c r="Z5" s="6"/>
-      <c r="AA5" s="6"/>
-      <c r="AB5" s="6"/>
-      <c r="AC5" s="6"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>24</v>
+        <v/>
+      </c>
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="7" t="n"/>
+      <c r="O5" s="7" t="n"/>
+      <c r="P5" s="7" t="n"/>
+      <c r="Q5" s="7" t="n"/>
+      <c r="R5" s="7" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
+      <c r="W5" s="6" t="n"/>
+      <c r="X5" s="6" t="n"/>
+      <c r="Y5" s="6" t="n"/>
+      <c r="Z5" s="6" t="n"/>
+      <c r="AA5" s="6" t="n"/>
+      <c r="AB5" s="6" t="n"/>
+      <c r="AC5" s="6" t="n"/>
+      <c r="AD5" s="6" t="n"/>
+      <c r="AE5" s="6" t="n"/>
+      <c r="AF5" s="6" t="n"/>
+      <c r="AG5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Customer agreements and incentives cost</t>
+        </is>
       </c>
       <c r="G6" s="3">
         <f>654-H6</f>
-        <v>309</v>
-      </c>
-      <c r="H6" s="3">
+        <v/>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>345</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="3" t="n">
         <v>342</v>
       </c>
       <c r="K6" s="3">
         <f>657-L6</f>
-        <v>315</v>
-      </c>
-      <c r="L6" s="3">
+        <v/>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>25</v>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Energy systems and product sales cost</t>
+        </is>
       </c>
       <c r="G7" s="3">
         <f>201-H7</f>
-        <v>97</v>
-      </c>
-      <c r="H7" s="3">
+        <v/>
+      </c>
+      <c r="H7" s="3" t="n">
         <v>104</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="3" t="n">
         <v>199</v>
       </c>
       <c r="K7" s="3">
         <f>387-L7</f>
-        <v>188</v>
-      </c>
-      <c r="L7" s="3">
+        <v/>
+      </c>
+      <c r="L7" s="3" t="n">
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>26</v>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S&amp;M</t>
+        </is>
       </c>
       <c r="G8" s="3">
         <f>298-H8</f>
-        <v>146</v>
-      </c>
-      <c r="H8" s="3">
+        <v/>
+      </c>
+      <c r="H8" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="n">
         <v>191</v>
       </c>
       <c r="K8" s="3">
         <f>369-L8</f>
-        <v>178</v>
-      </c>
-      <c r="L8" s="3">
+        <v/>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>29</v>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
       </c>
       <c r="G9" s="3">
         <f>18-H9</f>
-        <v>10</v>
-      </c>
-      <c r="H9" s="3">
+        <v/>
+      </c>
+      <c r="H9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="n">
         <v>10</v>
       </c>
       <c r="K9" s="3">
         <f>20-L9</f>
+        <v/>
+      </c>
+      <c r="L9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L9" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>27</v>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
       </c>
       <c r="G10" s="3">
         <f>129-H10</f>
-        <v>57</v>
-      </c>
-      <c r="H10" s="3">
+        <v/>
+      </c>
+      <c r="H10" s="3" t="n">
         <v>72</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="n">
         <v>93</v>
       </c>
       <c r="K10" s="3">
         <f>167-L10</f>
-        <v>74</v>
-      </c>
-      <c r="L10" s="3">
+        <v/>
+      </c>
+      <c r="L10" s="3" t="n">
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>28</v>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
       </c>
       <c r="G11" s="3">
-        <f t="shared" ref="G11:K11" si="0">SUM(G6:G10)</f>
-        <v>619</v>
+        <f>SUM(G6:G10)</f>
+        <v/>
       </c>
       <c r="H11" s="3">
-        <f t="shared" si="0"/>
-        <v>681</v>
+        <f>SUM(H6:H10)</f>
+        <v/>
       </c>
       <c r="I11" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>SUM(I6:I10)</f>
+        <v/>
       </c>
       <c r="J11" s="3">
         <f>SUM(J6:J10)</f>
-        <v>835</v>
+        <v/>
       </c>
       <c r="K11" s="3">
-        <f t="shared" si="0"/>
-        <v>765</v>
+        <f>SUM(K6:K10)</f>
+        <v/>
       </c>
       <c r="L11" s="3">
         <f>SUM(L6:L10)</f>
-        <v>835</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
       <c r="G12" s="7">
-        <f t="shared" ref="G12:K12" si="1">G5-G11</f>
-        <v>-115</v>
+        <f>G5-G11</f>
+        <v/>
       </c>
       <c r="H12" s="7">
-        <f t="shared" si="1"/>
-        <v>-112</v>
+        <f>H5-H11</f>
+        <v/>
       </c>
       <c r="I12" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>I5-I11</f>
+        <v/>
       </c>
       <c r="J12" s="7">
         <f>J5-J11</f>
-        <v>35</v>
+        <v/>
       </c>
       <c r="K12" s="7">
-        <f t="shared" si="1"/>
-        <v>-43</v>
+        <f>K5-K11</f>
+        <v/>
       </c>
       <c r="L12" s="7">
         <f>L5-L11</f>
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>34</v>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
       </c>
       <c r="G13" s="3">
         <f>-475-H13</f>
-        <v>-228</v>
-      </c>
-      <c r="H13" s="3">
+        <v/>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>-247</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="3" t="n">
         <v>-264</v>
       </c>
       <c r="K13" s="3">
         <f>-528-L13</f>
+        <v/>
+      </c>
+      <c r="L13" s="3" t="n">
         <v>-264</v>
       </c>
-      <c r="L13" s="3">
-        <v>-264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>35</v>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
       </c>
       <c r="G14" s="3">
         <f>-60-H14</f>
-        <v>-45</v>
-      </c>
-      <c r="H14" s="3">
+        <v/>
+      </c>
+      <c r="H14" s="3" t="n">
         <v>-15</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="n">
         <v>17</v>
       </c>
       <c r="K14" s="3">
         <f>35-L14</f>
-        <v>18</v>
-      </c>
-      <c r="L14" s="3">
+        <v/>
+      </c>
+      <c r="L14" s="3" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>EBT</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
       <c r="G15" s="7">
         <f>+G12+G13+G14</f>
-        <v>-388</v>
+        <v/>
       </c>
       <c r="H15" s="7">
-        <f t="shared" ref="H15:L15" si="2">+H12+H13+H14</f>
-        <v>-374</v>
+        <f>+H12+H13+H14</f>
+        <v/>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>+I12+I13+I14</f>
+        <v/>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="2"/>
-        <v>-212</v>
+        <f>+J12+J13+J14</f>
+        <v/>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="2"/>
-        <v>-289</v>
+        <f>+K12+K13+K14</f>
+        <v/>
       </c>
       <c r="L15" s="7">
-        <f t="shared" si="2"/>
-        <v>-212</v>
-      </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>36</v>
+        <f>+L12+L13+L14</f>
+        <v/>
+      </c>
+      <c r="M15" s="7" t="n"/>
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n"/>
+      <c r="P15" s="7" t="n"/>
+      <c r="Q15" s="7" t="n"/>
+      <c r="R15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
       </c>
       <c r="G16" s="3">
         <f>-205-H16</f>
-        <v>-110</v>
-      </c>
-      <c r="H16" s="3">
+        <v/>
+      </c>
+      <c r="H16" s="3" t="n">
         <v>-95</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="3" t="n">
         <v>-4</v>
       </c>
       <c r="K16" s="3">
         <f>-3-L16</f>
-        <v>1</v>
-      </c>
-      <c r="L16" s="3">
+        <v/>
+      </c>
+      <c r="L16" s="3" t="n">
         <v>-4</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>39</v>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Earnings</t>
+        </is>
       </c>
       <c r="G17" s="3">
         <f>+G15-G16</f>
-        <v>-278</v>
+        <v/>
       </c>
       <c r="H17" s="3">
-        <f t="shared" ref="H17:L17" si="3">+H15-H16</f>
-        <v>-279</v>
+        <f>+H15-H16</f>
+        <v/>
       </c>
       <c r="I17" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>+I15-I16</f>
+        <v/>
       </c>
       <c r="J17" s="3">
-        <f t="shared" si="3"/>
-        <v>-208</v>
+        <f>+J15-J16</f>
+        <v/>
       </c>
       <c r="K17" s="3">
-        <f t="shared" si="3"/>
-        <v>-290</v>
+        <f>+K15-K16</f>
+        <v/>
       </c>
       <c r="L17" s="3">
-        <f t="shared" si="3"/>
-        <v>-208</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>22</v>
+        <f>+L15-L16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Revenue y/y</t>
+        </is>
       </c>
       <c r="K22" s="4">
         <f>K5/G5-1</f>
-        <v>0.43253968253968256</v>
+        <v/>
       </c>
       <c r="L22" s="4">
         <f>L5/H5-1</f>
-        <v>0.52899824253075578</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="4" t="e">
-        <f t="shared" ref="C23:L23" si="4">C12/C5</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D23" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E23" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F23" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Operating margin</t>
+        </is>
+      </c>
+      <c r="C23" s="4">
+        <f>C12/C5</f>
+        <v/>
+      </c>
+      <c r="D23" s="4">
+        <f>D12/D5</f>
+        <v/>
+      </c>
+      <c r="E23" s="4">
+        <f>E12/E5</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>F12/F5</f>
+        <v/>
       </c>
       <c r="G23" s="4">
-        <f t="shared" si="4"/>
-        <v>-0.22817460317460317</v>
+        <f>G12/G5</f>
+        <v/>
       </c>
       <c r="H23" s="4">
-        <f t="shared" si="4"/>
-        <v>-0.19683655536028119</v>
-      </c>
-      <c r="I23" s="4" t="e">
-        <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <f>H12/H5</f>
+        <v/>
+      </c>
+      <c r="I23" s="4">
+        <f>I12/I5</f>
+        <v/>
       </c>
       <c r="J23" s="4">
-        <f t="shared" si="4"/>
-        <v>4.0229885057471264E-2</v>
+        <f>J12/J5</f>
+        <v/>
       </c>
       <c r="K23" s="4">
-        <f t="shared" si="4"/>
-        <v>-5.9556786703601108E-2</v>
+        <f>K12/K5</f>
+        <v/>
       </c>
       <c r="L23" s="4">
         <f>L12/L5</f>
-        <v>4.0229885057471264E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
-        <v>42</v>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Shares outstanding</t>
+        </is>
       </c>
       <c r="K24" s="3">
         <f>+(227*2)-L24</f>
-        <v>225</v>
-      </c>
-      <c r="L24" s="3">
+        <v/>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>229</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="4" t="e">
-        <f t="shared" ref="C26:L26" si="5">C16/C15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D26" s="4" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E26" s="4" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F26" s="4" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tax rate</t>
+        </is>
+      </c>
+      <c r="C26" s="4">
+        <f>C16/C15</f>
+        <v/>
+      </c>
+      <c r="D26" s="4">
+        <f>D16/D15</f>
+        <v/>
+      </c>
+      <c r="E26" s="4">
+        <f>E16/E15</f>
+        <v/>
+      </c>
+      <c r="F26" s="4">
+        <f>F16/F15</f>
+        <v/>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="5"/>
-        <v>0.28350515463917525</v>
+        <f>G16/G15</f>
+        <v/>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="5"/>
-        <v>0.25401069518716579</v>
-      </c>
-      <c r="I26" s="4" t="e">
-        <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <f>H16/H15</f>
+        <v/>
+      </c>
+      <c r="I26" s="4">
+        <f>I16/I15</f>
+        <v/>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="5"/>
-        <v>1.8867924528301886E-2</v>
+        <f>J16/J15</f>
+        <v/>
       </c>
       <c r="K26" s="4">
-        <f t="shared" si="5"/>
-        <v>-3.4602076124567475E-3</v>
+        <f>K16/K15</f>
+        <v/>
       </c>
       <c r="L26" s="4">
         <f>L16/L15</f>
-        <v>1.8867924528301886E-2</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{9C54FA0C-DCC4-496B-9899-E908EF8A3B26}"/>
+    <hyperlink ref="A1" location="Main!A1" display="Main"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J2" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
 </worksheet>
 </file>
--- a/RUN.xlsx
+++ b/RUN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD67134C-74CB-40B8-A6FA-84F54C4C6FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5645502E-B774-488D-8ABC-F46A7A3BC114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -825,7 +825,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BP26"/>
+  <dimension ref="A1:BZ26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="38.42578125" bestFit="1" customWidth="1"/>
@@ -833,12 +833,12 @@
     <col min="38" max="53" width="9.140625" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:78" x14ac:dyDescent="0.25">
       <c r="C2" s="9" t="s">
         <v>44</v>
       </c>
@@ -993,40 +993,70 @@
         <v>16</v>
       </c>
       <c r="BF2">
+        <v>2015</v>
+      </c>
+      <c r="BG2">
+        <v>2016</v>
+      </c>
+      <c r="BH2">
+        <v>2017</v>
+      </c>
+      <c r="BI2">
+        <v>2018</v>
+      </c>
+      <c r="BJ2">
+        <v>2019</v>
+      </c>
+      <c r="BK2">
+        <v>2020</v>
+      </c>
+      <c r="BL2">
+        <v>2021</v>
+      </c>
+      <c r="BM2">
+        <v>2022</v>
+      </c>
+      <c r="BN2">
+        <v>2023</v>
+      </c>
+      <c r="BO2">
+        <v>2024</v>
+      </c>
+      <c r="BP2">
         <v>2025</v>
       </c>
-      <c r="BG2">
+      <c r="BQ2">
         <v>2026</v>
       </c>
-      <c r="BH2">
+      <c r="BR2">
         <v>2027</v>
       </c>
-      <c r="BI2">
+      <c r="BS2">
         <v>2028</v>
       </c>
-      <c r="BJ2">
+      <c r="BT2">
         <v>2029</v>
       </c>
-      <c r="BK2">
+      <c r="BU2">
         <v>2030</v>
       </c>
-      <c r="BL2">
+      <c r="BV2">
         <v>2031</v>
       </c>
-      <c r="BM2">
+      <c r="BW2">
         <v>2032</v>
       </c>
-      <c r="BN2">
+      <c r="BX2">
         <v>2033</v>
       </c>
-      <c r="BO2">
+      <c r="BY2">
         <v>2034</v>
       </c>
-      <c r="BP2">
+      <c r="BZ2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>17</v>
       </c>
@@ -1048,7 +1078,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="4" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>18</v>
       </c>
@@ -1070,7 +1100,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="5" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>19</v>
       </c>
@@ -1155,8 +1185,18 @@
       <c r="BN5" s="6"/>
       <c r="BO5" s="6"/>
       <c r="BP5" s="6"/>
-    </row>
-    <row r="6" spans="1:68" x14ac:dyDescent="0.25">
+      <c r="BQ5" s="6"/>
+      <c r="BR5" s="6"/>
+      <c r="BS5" s="6"/>
+      <c r="BT5" s="6"/>
+      <c r="BU5" s="6"/>
+      <c r="BV5" s="6"/>
+      <c r="BW5" s="6"/>
+      <c r="BX5" s="6"/>
+      <c r="BY5" s="6"/>
+      <c r="BZ5" s="6"/>
+    </row>
+    <row r="6" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>20</v>
       </c>
@@ -1178,7 +1218,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="7" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>21</v>
       </c>
@@ -1200,7 +1240,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="8" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>22</v>
       </c>
@@ -1222,7 +1262,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="9" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>23</v>
       </c>
@@ -1244,7 +1284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>24</v>
       </c>
@@ -1266,7 +1306,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>25</v>
       </c>
@@ -1295,7 +1335,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="12" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>26</v>
       </c>
@@ -1363,7 +1403,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1385,7 +1425,7 @@
         <v>-264</v>
       </c>
     </row>
-    <row r="14" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>28</v>
       </c>
@@ -1407,7 +1447,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
         <v>29</v>
       </c>
@@ -1481,7 +1521,7 @@
       <c r="AZ15" s="7"/>
       <c r="BA15" s="7"/>
     </row>
-    <row r="16" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:78" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>30</v>
       </c>
